--- a/scripts/build/sheets_golden.xlsx
+++ b/scripts/build/sheets_golden.xlsx
@@ -10,7 +10,7 @@
     <sheet name="output" sheetId="3" r:id="rIdFrazaro3"/>
   </sheets>
   <definedNames>
-    <definedName name="Frazaro.Build">"Frazaro 0.9.0; sentences sha256:B191C71CDB782289B96678C59D4A71F0D0F2334483EA20F172B1D7859BC1D242 over 664 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.9.1; sentences sha256:B191C71CDB782289B96678C59D4A71F0D0F2334483EA20F172B1D7859BC1D242 over 664 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>

--- a/scripts/build/sheets_golden.xlsx
+++ b/scripts/build/sheets_golden.xlsx
@@ -10,7 +10,7 @@
     <sheet name="output" sheetId="3" r:id="rIdFrazaro3"/>
   </sheets>
   <definedNames>
-    <definedName name="Frazaro.Build">"Frazaro 0.9.1; sentences sha256:B191C71CDB782289B96678C59D4A71F0D0F2334483EA20F172B1D7859BC1D242 over 664 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.9.2; sentences sha256:B191C71CDB782289B96678C59D4A71F0D0F2334483EA20F172B1D7859BC1D242 over 664 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>

--- a/scripts/build/sheets_golden.xlsx
+++ b/scripts/build/sheets_golden.xlsx
@@ -10,7 +10,7 @@
     <sheet name="output" sheetId="3" r:id="rIdFrazaro3"/>
   </sheets>
   <definedNames>
-    <definedName name="Frazaro.Build">"Frazaro 0.9.2; sentences sha256:B191C71CDB782289B96678C59D4A71F0D0F2334483EA20F172B1D7859BC1D242 over 664 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.9.3; sentences sha256:B191C71CDB782289B96678C59D4A71F0D0F2334483EA20F172B1D7859BC1D242 over 664 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>

--- a/scripts/build/sheets_golden.xlsx
+++ b/scripts/build/sheets_golden.xlsx
@@ -10,7 +10,7 @@
     <sheet name="output" sheetId="3" r:id="rIdFrazaro3"/>
   </sheets>
   <definedNames>
-    <definedName name="Frazaro.Build">"Frazaro 0.9.3; sentences sha256:B191C71CDB782289B96678C59D4A71F0D0F2334483EA20F172B1D7859BC1D242 over 664 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.9.4; sentences sha256:B191C71CDB782289B96678C59D4A71F0D0F2334483EA20F172B1D7859BC1D242 over 664 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>

--- a/scripts/build/sheets_golden.xlsx
+++ b/scripts/build/sheets_golden.xlsx
@@ -10,7 +10,7 @@
     <sheet name="output" sheetId="3" r:id="rIdFrazaro3"/>
   </sheets>
   <definedNames>
-    <definedName name="Frazaro.Build">"Frazaro 0.9.4; sentences sha256:B191C71CDB782289B96678C59D4A71F0D0F2334483EA20F172B1D7859BC1D242 over 664 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.10.0; sentences sha256:B191C71CDB782289B96678C59D4A71F0D0F2334483EA20F172B1D7859BC1D242 over 664 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>

--- a/scripts/build/sheets_golden.xlsx
+++ b/scripts/build/sheets_golden.xlsx
@@ -10,7 +10,7 @@
     <sheet name="output" sheetId="3" r:id="rIdFrazaro3"/>
   </sheets>
   <definedNames>
-    <definedName name="Frazaro.Build">"Frazaro 0.10.0; sentences sha256:B191C71CDB782289B96678C59D4A71F0D0F2334483EA20F172B1D7859BC1D242 over 664 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.10.1; sentences sha256:B191C71CDB782289B96678C59D4A71F0D0F2334483EA20F172B1D7859BC1D242 over 664 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>

--- a/scripts/build/sheets_golden.xlsx
+++ b/scripts/build/sheets_golden.xlsx
@@ -10,7 +10,7 @@
     <sheet name="output" sheetId="3" r:id="rIdFrazaro3"/>
   </sheets>
   <definedNames>
-    <definedName name="Frazaro.Build">"Frazaro 0.10.1; sentences sha256:B191C71CDB782289B96678C59D4A71F0D0F2334483EA20F172B1D7859BC1D242 over 664 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.11.0; sentences sha256:B191C71CDB782289B96678C59D4A71F0D0F2334483EA20F172B1D7859BC1D242 over 664 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>

--- a/scripts/build/sheets_golden.xlsx
+++ b/scripts/build/sheets_golden.xlsx
@@ -10,7 +10,7 @@
     <sheet name="output" sheetId="3" r:id="rIdFrazaro3"/>
   </sheets>
   <definedNames>
-    <definedName name="Frazaro.Build">"Frazaro 0.11.0; sentences sha256:B191C71CDB782289B96678C59D4A71F0D0F2334483EA20F172B1D7859BC1D242 over 664 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.12.0; sentences sha256:B191C71CDB782289B96678C59D4A71F0D0F2334483EA20F172B1D7859BC1D242 over 664 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
